--- a/AAII_Financials/Quarterly/RBGLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RBGLY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="92">
   <si>
     <t>RBGLY</t>
   </si>
@@ -656,85 +656,87 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
@@ -747,8 +749,14 @@
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -809,8 +817,14 @@
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -871,8 +885,14 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -933,8 +953,14 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -957,8 +983,10 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1019,8 +1047,14 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1081,8 +1115,14 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1143,8 +1183,14 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1205,8 +1251,14 @@
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1226,8 +1278,10 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1288,8 +1342,14 @@
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1350,8 +1410,14 @@
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1374,8 +1440,10 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1436,8 +1504,14 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1498,8 +1572,14 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1542,26 +1622,32 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
+        <v>0</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1622,8 +1708,14 @@
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1684,8 +1776,14 @@
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1746,8 +1844,14 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1808,8 +1912,14 @@
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1870,8 +1980,14 @@
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1932,8 +2048,14 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1994,8 +2116,14 @@
       <c r="V29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2056,8 +2184,14 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2118,8 +2252,14 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2180,8 +2320,14 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2242,8 +2388,14 @@
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2304,8 +2456,14 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2366,61 +2524,67 @@
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2433,8 +2597,14 @@
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2457,8 +2627,10 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2481,70 +2653,78 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1164900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1159400</v>
+      </c>
+      <c r="F41" s="3">
         <v>2627200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>2623900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1319400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1244200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1101700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1179500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1246100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1245300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1766700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1692600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1305100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1270500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1394100</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S41" s="3">
-        <v>0</v>
+      <c r="S41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
+      <c r="U41" s="3">
+        <v>0</v>
       </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2596,451 +2776,499 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U42" s="3" t="s">
-        <v>3</v>
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+      <c r="U42" s="3">
+        <v>0</v>
       </c>
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2982600</v>
+      </c>
+      <c r="E43" s="3">
+        <v>2968400</v>
+      </c>
+      <c r="F43" s="3">
         <v>2761800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>2758300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>3023700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>2851500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>2520100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>2698000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>2847300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>2845500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>2612500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>2502900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>2835100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>2760000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>2582100</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S43" s="3">
-        <v>0</v>
+      <c r="S43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
+      <c r="U43" s="3">
+        <v>0</v>
       </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2051200</v>
+      </c>
+      <c r="E44" s="3">
+        <v>2041400</v>
+      </c>
+      <c r="F44" s="3">
         <v>1982500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1980000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>2216700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>2090500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1899200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>2033200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>1998100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1996800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>2085100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>1997700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>2108200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>2052400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>2198900</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S44" s="3">
-        <v>0</v>
+      <c r="S44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>3</v>
+      <c r="U44" s="3">
+        <v>0</v>
       </c>
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>232200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>231100</v>
+      </c>
+      <c r="F45" s="3">
         <v>37700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>37600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>109600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>103400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>81400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>87100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>82100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>82100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>173200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>166000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>104200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>101400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>79500</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S45" s="3">
-        <v>0</v>
+      <c r="S45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
+      <c r="U45" s="3">
+        <v>0</v>
       </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6430900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>6400300</v>
+      </c>
+      <c r="F46" s="3">
         <v>7584100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>7574500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>6669400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>6289500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>5756400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>6162700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>6173600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>6169600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>6753500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>6470100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>6352700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>6184400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>6367900</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S46" s="3">
-        <v>0</v>
+      <c r="S46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
+      <c r="U46" s="3">
+        <v>0</v>
       </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>209600</v>
+      </c>
+      <c r="E47" s="3">
+        <v>208600</v>
+      </c>
+      <c r="F47" s="3">
         <v>218000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>217800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>178100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>168000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>135200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>144800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>184500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>184400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>150300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>144000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>100400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>97700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>154200</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S47" s="3">
-        <v>0</v>
+      <c r="S47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
+      <c r="U47" s="3">
+        <v>0</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3419100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>3402900</v>
+      </c>
+      <c r="F48" s="3">
         <v>3375500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>3371200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>3155200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>2975500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>2985800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>3196600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>2942100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>2940200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>3055700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>2927500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>3002900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>2923300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>2979700</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S48" s="3">
-        <v>0</v>
+      <c r="S48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
+      <c r="U48" s="3">
+        <v>0</v>
       </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>21052100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>20951900</v>
+      </c>
+      <c r="F49" s="3">
         <v>21279900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>21253100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>22896300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>21592000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>21990100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>23542400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>23279000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>23264000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>23676600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>22683200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>24602600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>23950900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>24342400</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S49" s="3">
-        <v>0</v>
+      <c r="S49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
+      <c r="U49" s="3">
+        <v>0</v>
       </c>
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3101,8 +3329,14 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3163,70 +3397,82 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>887600</v>
+      </c>
+      <c r="E52" s="3">
+        <v>883400</v>
+      </c>
+      <c r="F52" s="3">
         <v>594900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>594100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>515100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>485800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>499500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>534800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>467600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>467300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>563000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>539400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>602400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>586400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>492800</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S52" s="3">
-        <v>0</v>
+      <c r="S52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
+      <c r="U52" s="3">
+        <v>0</v>
       </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3287,70 +3533,82 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>32408100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>32253800</v>
+      </c>
+      <c r="F54" s="3">
         <v>33738900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>33696300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>33727900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>31806600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>31671200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>33907000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>33374200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>33352700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>34564600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>33114500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>34965900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>34039700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>34631000</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S54" s="3">
-        <v>0</v>
+      <c r="S54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
+      <c r="U54" s="3">
+        <v>0</v>
       </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3373,8 +3631,10 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3397,304 +3657,330 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6391100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>6360700</v>
+      </c>
+      <c r="F57" s="3">
         <v>2862700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2859100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>6998200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>6599600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2839400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>3039800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>6464300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>6460100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>2794600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>2677400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>6327300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>6159700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>2850800</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S57" s="3">
-        <v>0</v>
+      <c r="S57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
+      <c r="U57" s="3">
+        <v>0</v>
       </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3575700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>3558700</v>
+      </c>
+      <c r="F58" s="3">
         <v>1090200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1088800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>4017000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>3788200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1781500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1907300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1353500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1352600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>2138600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>2048900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>4282600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>4169100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>2073600</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S58" s="3">
-        <v>0</v>
+      <c r="S58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
+      <c r="U58" s="3">
+        <v>0</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>887600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>883400</v>
+      </c>
+      <c r="F59" s="3">
         <v>1869400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1867100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>979600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>923800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>2079400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2226200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1081800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1081100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>2036700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1802400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1162800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1132000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1567600</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S59" s="3">
-        <v>0</v>
+      <c r="S59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
+      <c r="U59" s="3">
+        <v>0</v>
       </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10854500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>10802800</v>
+      </c>
+      <c r="F60" s="3">
         <v>8950200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>8938900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>11994800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>11311500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>9944000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>10646000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>8899600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>8893900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>10620600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>10175000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>11772600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>11460800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>10050000</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S60" s="3">
-        <v>0</v>
+      <c r="S60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
+      <c r="U60" s="3">
+        <v>0</v>
       </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10029200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>9981400</v>
+      </c>
+      <c r="F61" s="3">
         <v>10383600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>10370500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>8864200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>8359300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>9274300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>9929000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>10152000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>10145500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>8973600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>8597100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>6702200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>6524600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>8929500</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3707,70 +3993,82 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>196400</v>
+      </c>
+      <c r="E62" s="3">
+        <v>195400</v>
+      </c>
+      <c r="F62" s="3">
         <v>188400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>188200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>174000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>164100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>179000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>191700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>161800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>161700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>193600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>185500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>781500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>760800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>277100</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S62" s="3">
-        <v>0</v>
+      <c r="S62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
+      <c r="U62" s="3">
+        <v>0</v>
       </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3831,8 +4129,14 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3893,8 +4197,14 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3955,70 +4265,82 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>24838800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>24720600</v>
+      </c>
+      <c r="F66" s="3">
         <v>23266500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>23237100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>25030800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>23605000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>23258300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>24900100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>23148900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>23134000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>23777200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>22779600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>23264400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>22648200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>23205000</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S66" s="3">
-        <v>0</v>
+      <c r="S66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
+      <c r="U66" s="3">
+        <v>0</v>
       </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4041,8 +4363,10 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4103,8 +4427,14 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4165,8 +4495,14 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4218,17 +4554,23 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-      <c r="T70" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U70" s="3" t="s">
-        <v>3</v>
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
+        <v>0</v>
       </c>
       <c r="V70" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4289,70 +4631,82 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>28143800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>28009900</v>
+      </c>
+      <c r="F72" s="3">
         <v>31492600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>31452800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>30385000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>28654100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>27529800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>29473300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>29393300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>29374300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>29817300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>28566400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>30480000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>29672700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>28481200</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S72" s="3">
-        <v>0</v>
+      <c r="S72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
+      <c r="U72" s="3">
+        <v>0</v>
       </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4413,8 +4767,14 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4475,8 +4835,14 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4537,70 +4903,82 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7522900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>7487100</v>
+      </c>
+      <c r="F76" s="3">
         <v>10425300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>10412100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>8647800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>8155100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>8386600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>8978700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>10196300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>10189700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>10760700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>10309200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>11674800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>11365500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>11377800</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S76" s="3">
-        <v>0</v>
+      <c r="S76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
+      <c r="U76" s="3">
+        <v>0</v>
       </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4661,61 +5039,67 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4728,8 +5112,14 @@
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4790,8 +5180,14 @@
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4814,70 +5210,78 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F83" s="3">
+      <c r="D83" s="3">
+        <v>161000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>151800</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3">
         <v>149800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>149700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>82200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>78700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>148700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>144700</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3">
         <v>135500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>146600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>100200</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S83" s="3">
-        <v>0</v>
+      <c r="S83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
+      <c r="U83" s="3">
+        <v>0</v>
       </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4938,8 +5342,14 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5000,8 +5410,14 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5062,8 +5478,14 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5124,8 +5546,14 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5186,70 +5614,82 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>407300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>405400</v>
+      </c>
+      <c r="F89" s="3">
         <v>999300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>998100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>556200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>524600</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L89" s="3">
         <v>620500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>620100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>1083300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>1037900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>594100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>578400</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
+      <c r="S89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
+      <c r="U89" s="3">
+        <v>0</v>
       </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5272,70 +5712,78 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-115400</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-114900</v>
+      </c>
+      <c r="F91" s="3">
         <v>-254400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-254100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-108200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-102100</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="J91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L91" s="3">
         <v>-79600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-79600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-129900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-124500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-91500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-89100</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
+      <c r="R91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5396,8 +5844,14 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5458,70 +5912,82 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-180400</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-179600</v>
+      </c>
+      <c r="F94" s="3">
         <v>932000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>930900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-130200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-122700</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3">
         <v>-67000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-66900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-178300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-170800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-118200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-115100</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
+      <c r="S94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
+      <c r="U94" s="3">
+        <v>0</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5544,55 +6010,57 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1592100</v>
+      </c>
+      <c r="E96" s="3">
+        <v>1584600</v>
+      </c>
+      <c r="F96" s="3">
         <v>385600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>385100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>568600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>536200</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3">
         <v>518200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>517800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>349600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>335000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>502000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>488700</v>
       </c>
-      <c r="P96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
-        <v>0</v>
+      <c r="R96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S96" s="3">
         <v>0</v>
@@ -5606,8 +6074,14 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5668,8 +6142,14 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5730,8 +6210,14 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5792,190 +6278,214 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-865700</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-861600</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1274600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-1273000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-369200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-348200</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3">
         <v>-782300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-781800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-664900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-637000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-486100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-473200</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
+      <c r="S100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
+      <c r="U100" s="3">
+        <v>0</v>
       </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F101" s="3">
+      <c r="D101" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3">
         <v>-22100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-22100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-14600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-14000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-72400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-70500</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3">
         <v>29200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>31500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S101" s="3">
-        <v>0</v>
+      <c r="S101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>3</v>
+      <c r="U101" s="3">
+        <v>0</v>
       </c>
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-636200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-633200</v>
+      </c>
+      <c r="F102" s="3">
         <v>671600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>670800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>51400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>48500</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-250900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-250700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>225500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>216000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-82600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-80400</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S102" s="3">
-        <v>0</v>
+      <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
+      <c r="U102" s="3">
+        <v>0</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
